--- a/exports/TECHM_full_report.xlsx
+++ b/exports/TECHM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.61</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1564.5</v>
+        <v>1549.2</v>
       </c>
       <c r="I2" t="n">
         <v>1561.3163403</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.57</v>
+        <v>-4.51</v>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>5.62</v>
       </c>
       <c r="M2" t="n">
         <v>0.83</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.66</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44623.38541666666</v>
+        <v>44623.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1338.3</v>
+        <v>1341.5</v>
       </c>
       <c r="I3" t="n">
         <v>1339.900928744682</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>13.61</v>
+        <v>13.41</v>
       </c>
       <c r="L3" t="n">
         <v>1.85</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.74</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1409</v>
+        <v>1387</v>
       </c>
       <c r="I4" t="n">
         <v>1392.430023361787</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>5.03</v>
+        <v>3.39</v>
       </c>
       <c r="L4" t="n">
         <v>2.18</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.54</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1183.1</v>
+        <v>1200.7</v>
       </c>
       <c r="I5" t="n">
         <v>1196.509316965638</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K5" t="n">
-        <v>14.7</v>
+        <v>13.43</v>
       </c>
       <c r="L5" t="n">
         <v>3.14</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.56</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44694.38541666666</v>
+        <v>44694.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>1141</v>
+        <v>1122.8</v>
       </c>
       <c r="I6" t="n">
         <v>1131.289942138845</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.97</v>
+        <v>-6.49</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.96</v>
       </c>
       <c r="M6" t="n">
         <v>1.96</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>8.74</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1049.1</v>
+        <v>1089.1</v>
       </c>
       <c r="I7" t="n">
         <v>1067.267716336373</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>6.56</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="N7" t="n">
         <v>4.09</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1035.7</v>
+        <v>986.9</v>
       </c>
       <c r="I8" t="n">
         <v>1025.31196094511</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.9</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>5.77</v>
+        <v>9.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.88</v>
+        <v>2.66</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>5.08</v>
       </c>
       <c r="O8" t="n">
         <v>3.68</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.43</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>938.5</v>
+        <v>966.5</v>
       </c>
       <c r="I9" t="n">
         <v>948.2007215653463</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>2.07</v>
       </c>
       <c r="L9" t="n">
         <v>2.46</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.33</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1003.4</v>
+        <v>990.4</v>
       </c>
       <c r="I10" t="n">
         <v>994.4137587771074</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K10" t="n">
-        <v>3.82</v>
+        <v>2.47</v>
       </c>
       <c r="L10" t="n">
         <v>4.53</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>4.81</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44812.55208333334</v>
+        <v>44813.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1016.6</v>
+        <v>1037.3</v>
       </c>
       <c r="I11" t="n">
         <v>1027.025620391332</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.65</v>
+        <v>-4.74</v>
       </c>
       <c r="L11" t="n">
-        <v>3.37</v>
+        <v>4.86</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="N11" t="n">
         <v>3.9</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>6.03</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44818.55208333334</v>
+        <v>44819.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1037.5</v>
+        <v>1012.6</v>
       </c>
       <c r="I12" t="n">
         <v>1021.586101056739</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02</v>
+        <v>-2.38</v>
       </c>
       <c r="L12" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="M12" t="n">
         <v>3.06</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44858.76041666666</v>
+        <v>44859.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>975.8</v>
+        <v>1008.2</v>
       </c>
       <c r="I13" t="n">
         <v>989.1630462251302</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39.375</v>
+        <v>40</v>
       </c>
       <c r="K13" t="n">
-        <v>3.63</v>
+        <v>0.43</v>
       </c>
       <c r="L13" t="n">
         <v>3.62</v>
@@ -1182,7 +1337,7 @@
         <v>2.24</v>
       </c>
       <c r="N13" t="n">
-        <v>2.61</v>
+        <v>3.49</v>
       </c>
       <c r="O13" t="n">
         <v>-2.85</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.03</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44874.38541666666</v>
+        <v>44874.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>964.8</v>
+        <v>956.2</v>
       </c>
       <c r="I14" t="n">
         <v>963.8098298276366</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.3</v>
+        <v>-5.16</v>
       </c>
       <c r="L14" t="n">
-        <v>4.73</v>
+        <v>5.34</v>
       </c>
       <c r="M14" t="n">
         <v>0.89</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>5.64</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44890.38541666666</v>
+        <v>44890.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>998</v>
+        <v>1003.8</v>
       </c>
       <c r="I15" t="n">
         <v>1002.26327747184</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.37</v>
+        <v>-4.98</v>
       </c>
       <c r="L15" t="n">
-        <v>4.81</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
         <v>3.03</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>4.17</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1001.2</v>
+        <v>967.8</v>
       </c>
       <c r="I16" t="n">
         <v>999.7314321588691</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.26</v>
+        <v>-3.59</v>
       </c>
       <c r="L16" t="n">
-        <v>1.29</v>
+        <v>4.07</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>3.57</v>
       </c>
       <c r="O16" t="n">
         <v>0.72</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.93</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44939.55208333334</v>
+        <v>44942.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>933.1</v>
+        <v>960.5</v>
       </c>
       <c r="I17" t="n">
         <v>954.8004619998422</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K17" t="n">
-        <v>3.59</v>
+        <v>0.75</v>
       </c>
       <c r="L17" t="n">
         <v>3.51</v>
@@ -1410,7 +1613,7 @@
         <v>1.24</v>
       </c>
       <c r="N17" t="n">
-        <v>2.81</v>
+        <v>3.19</v>
       </c>
       <c r="O17" t="n">
         <v>-3.57</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.56</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>978.7</v>
+        <v>962</v>
       </c>
       <c r="I18" t="n">
         <v>965.9145924181839</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>1.89</v>
+        <v>0.16</v>
       </c>
       <c r="L18" t="n">
         <v>2.82</v>
@@ -1467,7 +1682,7 @@
         <v>0.36</v>
       </c>
       <c r="N18" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="O18" t="n">
         <v>3.19</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.97</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44971.55208333334</v>
+        <v>44972.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>942</v>
+        <v>971.5</v>
       </c>
       <c r="I19" t="n">
         <v>967.5037902011536</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>2.08</v>
+        <v>-0.99</v>
       </c>
       <c r="L19" t="n">
         <v>2.45</v>
@@ -1524,7 +1751,7 @@
         <v>0.92</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>5.88</v>
       </c>
       <c r="O19" t="n">
         <v>-1.81</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.06</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44991.55208333334</v>
+        <v>44993.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1014.8</v>
+        <v>1006.9</v>
       </c>
       <c r="I20" t="n">
         <v>1009.025736043214</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>4.46</v>
+        <v>3.64</v>
       </c>
       <c r="L20" t="n">
         <v>3.42</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.62</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>989.2</v>
+        <v>1066.3</v>
       </c>
       <c r="I21" t="n">
         <v>1025.11966229772</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>1.76</v>
+        <v>-5.9</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3</v>
+        <v>6.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0.15</v>
+        <v>7.03</v>
       </c>
       <c r="O21" t="n">
         <v>-0.88</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.27</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45012.55208333334</v>
+        <v>45013.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1027</v>
+        <v>995.7</v>
       </c>
       <c r="I22" t="n">
         <v>999.4110735388465</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.69</v>
+        <v>-6.62</v>
       </c>
       <c r="L22" t="n">
-        <v>4.98</v>
+        <v>6.8</v>
       </c>
       <c r="M22" t="n">
         <v>1.21</v>
       </c>
       <c r="N22" t="n">
-        <v>1.73</v>
+        <v>2.52</v>
       </c>
       <c r="O22" t="n">
         <v>7.03</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.3</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>951.7</v>
+        <v>984.6</v>
       </c>
       <c r="I23" t="n">
         <v>963.5987051890077</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>4.42</v>
+        <v>1.11</v>
       </c>
       <c r="L23" t="n">
         <v>4.69</v>
@@ -1752,7 +2027,7 @@
         <v>1.14</v>
       </c>
       <c r="N23" t="n">
-        <v>2.19</v>
+        <v>3.09</v>
       </c>
       <c r="O23" t="n">
         <v>-2.52</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.51</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45082.55208333334</v>
+        <v>45083.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1036.7</v>
+        <v>1009.2</v>
       </c>
       <c r="I24" t="n">
         <v>1010.487086839474</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K24" t="n">
-        <v>5.29</v>
+        <v>2.5</v>
       </c>
       <c r="L24" t="n">
         <v>3.52</v>
@@ -1809,7 +2096,7 @@
         <v>1.28</v>
       </c>
       <c r="N24" t="n">
-        <v>1.45</v>
+        <v>2.04</v>
       </c>
       <c r="O24" t="n">
         <v>3.09</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>5.24</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45096.55208333334</v>
+        <v>45097.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1019.8</v>
+        <v>1034.3</v>
       </c>
       <c r="I25" t="n">
         <v>1034.216784598941</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.05</v>
+        <v>-2.49</v>
       </c>
       <c r="L25" t="n">
-        <v>1.86</v>
+        <v>2.72</v>
       </c>
       <c r="M25" t="n">
         <v>0.57</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.55</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45128.55208333334</v>
+        <v>45131.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1118.4</v>
+        <v>1112.5</v>
       </c>
       <c r="I26" t="n">
         <v>1112.851885624109</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>8.130000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="L26" t="n">
         <v>1.89</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>6.23</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45141.55208333334</v>
+        <v>45142.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1065.2</v>
+        <v>1093</v>
       </c>
       <c r="I27" t="n">
         <v>1084.689097406672</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
-        <v>4.25</v>
+        <v>1.75</v>
       </c>
       <c r="L27" t="n">
         <v>1.18</v>
       </c>
       <c r="M27" t="n">
-        <v>0.53</v>
+        <v>1.17</v>
       </c>
       <c r="N27" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="O27" t="n">
         <v>-3.29</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>7.28</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1208</v>
+        <v>1159.6</v>
       </c>
       <c r="I28" t="n">
         <v>1174.891920847917</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K28" t="n">
-        <v>10.52</v>
+        <v>6.09</v>
       </c>
       <c r="L28" t="n">
         <v>2.37</v>
       </c>
       <c r="M28" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="N28" t="n">
-        <v>1.84</v>
+        <v>4.35</v>
       </c>
       <c r="O28" t="n">
         <v>2.89</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>6.4</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1055.9</v>
+        <v>1093.4</v>
       </c>
       <c r="I29" t="n">
         <v>1085.212192405193</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K29" t="n">
-        <v>8.94</v>
+        <v>5.71</v>
       </c>
       <c r="L29" t="n">
         <v>2.85</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="O29" t="n">
         <v>-4.35</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.75</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45294.55208333334</v>
+        <v>45295.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1162.5</v>
+        <v>1155</v>
       </c>
       <c r="I30" t="n">
         <v>1160.731993226828</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K30" t="n">
-        <v>6.32</v>
+        <v>5.63</v>
       </c>
       <c r="L30" t="n">
         <v>2.34</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.99</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45302.55208333334</v>
+        <v>45303.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1168.7</v>
+        <v>1219.9</v>
       </c>
       <c r="I31" t="n">
         <v>1206.424263114338</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.19</v>
+        <v>-5.62</v>
       </c>
       <c r="L31" t="n">
-        <v>3.08</v>
+        <v>6.15</v>
       </c>
       <c r="M31" t="n">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="N31" t="n">
-        <v>1.29</v>
+        <v>4.83</v>
       </c>
       <c r="O31" t="n">
         <v>0.53</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.38</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45323.38541666666</v>
+        <v>45323.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1234.3</v>
+        <v>1230.2</v>
       </c>
       <c r="I32" t="n">
         <v>1230.206779681074</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>1.18</v>
+        <v>0.84</v>
       </c>
       <c r="L32" t="n">
         <v>2.78</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>5.76</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1113</v>
+        <v>1204.6</v>
       </c>
       <c r="I33" t="n">
         <v>1153.93115806599</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>84</v>
+        <v>84.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>9.529999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="L33" t="n">
         <v>3.83</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>5.09</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>7.72</v>
       </c>
       <c r="O33" t="n">
         <v>-1.28</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.76</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45441.38541666666</v>
+        <v>45441.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1211.1</v>
+        <v>1204.9</v>
       </c>
       <c r="I34" t="n">
         <v>1205.243499413948</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>0.54</v>
+        <v>0.02</v>
       </c>
       <c r="L34" t="n">
         <v>3.62</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>4.2</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45448.55208333334</v>
+        <v>45449.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1186.9</v>
+        <v>1231.9</v>
       </c>
       <c r="I35" t="n">
         <v>1209.774512086279</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>1.49</v>
+        <v>-2.24</v>
       </c>
       <c r="L35" t="n">
-        <v>0.62</v>
+        <v>2.71</v>
       </c>
       <c r="M35" t="n">
         <v>1.89</v>
       </c>
       <c r="N35" t="n">
-        <v>1.64</v>
+        <v>4.44</v>
       </c>
       <c r="O35" t="n">
         <v>-2.1</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1441.5</v>
+        <v>1389.6</v>
       </c>
       <c r="I36" t="n">
         <v>1412.757115524804</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K36" t="n">
-        <v>17.01</v>
+        <v>12.8</v>
       </c>
       <c r="L36" t="n">
         <v>3.17</v>
       </c>
       <c r="M36" t="n">
-        <v>0.97</v>
+        <v>2.39</v>
       </c>
       <c r="N36" t="n">
-        <v>2.32</v>
+        <v>3.38</v>
       </c>
       <c r="O36" t="n">
         <v>4.44</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.77</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1460.2</v>
+        <v>1503.2</v>
       </c>
       <c r="I37" t="n">
         <v>1479.473023853759</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.08</v>
+        <v>-8.18</v>
       </c>
       <c r="L37" t="n">
-        <v>5.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="O37" t="n">
         <v>-3.38</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.27</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1538.2</v>
+        <v>1506.9</v>
       </c>
       <c r="I38" t="n">
         <v>1522.256399627402</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K38" t="n">
-        <v>2.33</v>
+        <v>0.25</v>
       </c>
       <c r="L38" t="n">
         <v>2.49</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.25</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45574.38541666666</v>
+        <v>45574.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1582.6</v>
+        <v>1587</v>
       </c>
       <c r="I39" t="n">
         <v>1582.769099207985</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.02</v>
+        <v>-5.32</v>
       </c>
       <c r="L39" t="n">
         <v>6.07</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.98</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45595.55208333334</v>
+        <v>45596.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1613.8</v>
+        <v>1536.7</v>
       </c>
       <c r="I40" t="n">
         <v>1578.151708870206</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>1.69</v>
+        <v>-3.17</v>
       </c>
       <c r="L40" t="n">
-        <v>3.32</v>
+        <v>3.77</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7</v>
+        <v>1.15</v>
       </c>
       <c r="N40" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
         <v>1.82</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.64</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1605.2</v>
+        <v>1637.2</v>
       </c>
       <c r="I41" t="n">
         <v>1622.518707751188</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.46</v>
+        <v>-6.54</v>
       </c>
       <c r="L41" t="n">
         <v>6.85</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.58</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1677.6</v>
+        <v>1633.2</v>
       </c>
       <c r="I42" t="n">
         <v>1652.601933948025</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K42" t="n">
-        <v>2.47</v>
+        <v>-0.24</v>
       </c>
       <c r="L42" t="n">
         <v>4.51</v>
@@ -2835,7 +3338,7 @@
         <v>2.06</v>
       </c>
       <c r="N42" t="n">
-        <v>2.23</v>
+        <v>3.81</v>
       </c>
       <c r="O42" t="n">
         <v>1.67</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.52</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45680.55208333334</v>
+        <v>45681.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1637.4</v>
+        <v>1649.2</v>
       </c>
       <c r="I43" t="n">
         <v>1648.465813615019</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.26</v>
+        <v>-0.98</v>
       </c>
       <c r="L43" t="n">
         <v>3.95</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.29</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45712.38541666666</v>
+        <v>45712.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1558.6</v>
+        <v>1542.8</v>
       </c>
       <c r="I44" t="n">
         <v>1555.694600372282</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.49</v>
+        <v>-6.45</v>
       </c>
       <c r="L44" t="n">
-        <v>6.84</v>
+        <v>6.89</v>
       </c>
       <c r="M44" t="n">
         <v>0.98</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>4.89</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1248.9</v>
+        <v>1323.6</v>
       </c>
       <c r="I45" t="n">
         <v>1283.608363101739</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>52</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>19.05</v>
+        <v>14.21</v>
       </c>
       <c r="L45" t="n">
         <v>1.06</v>
@@ -3006,7 +3545,7 @@
         <v>2.28</v>
       </c>
       <c r="N45" t="n">
-        <v>3.48</v>
+        <v>5.3</v>
       </c>
       <c r="O45" t="n">
         <v>-2.09</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.03</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1503.3</v>
+        <v>1481.6</v>
       </c>
       <c r="I46" t="n">
         <v>1493.575618929697</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K46" t="n">
-        <v>13.58</v>
+        <v>11.94</v>
       </c>
       <c r="L46" t="n">
         <v>5.77</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>4.81</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45817.55208333334</v>
+        <v>45818.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1510.5</v>
+        <v>1546.6</v>
       </c>
       <c r="I47" t="n">
         <v>1535.405745788222</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.95</v>
+        <v>-4.39</v>
       </c>
       <c r="L47" t="n">
-        <v>2.81</v>
+        <v>5.53</v>
       </c>
       <c r="M47" t="n">
         <v>0.32</v>
       </c>
       <c r="N47" t="n">
-        <v>1.1</v>
+        <v>2.21</v>
       </c>
       <c r="O47" t="n">
         <v>-1.24</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.42</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45847.38541666666</v>
+        <v>45847.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1573.3</v>
+        <v>1571.5</v>
       </c>
       <c r="I48" t="n">
         <v>1572.953399873278</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="L48" t="n">
         <v>2.28</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>3.8</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1443.5</v>
+        <v>1475.3</v>
       </c>
       <c r="I49" t="n">
         <v>1456.61505181957</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>8.15</v>
+        <v>6.12</v>
       </c>
       <c r="L49" t="n">
         <v>0.57</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>5.8</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45908.38541666666</v>
+        <v>45908.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1431.5</v>
+        <v>1423</v>
       </c>
       <c r="I50" t="n">
         <v>1429.583027664533</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.97</v>
+        <v>-3.55</v>
       </c>
       <c r="L50" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="M50" t="n">
         <v>0.77</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>3.97</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1458.6</v>
+        <v>1490.1</v>
       </c>
       <c r="I51" t="n">
         <v>1479.505666873868</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.5</v>
+        <v>-4.72</v>
       </c>
       <c r="L51" t="n">
-        <v>2.74</v>
+        <v>5.21</v>
       </c>
       <c r="M51" t="n">
         <v>0.46</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>4.76</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1517.6</v>
+        <v>1457.7</v>
       </c>
       <c r="I52" t="n">
         <v>1465.089537724967</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K52" t="n">
-        <v>1.85</v>
+        <v>-2.17</v>
       </c>
       <c r="L52" t="n">
-        <v>1.76</v>
+        <v>4.94</v>
       </c>
       <c r="M52" t="n">
-        <v>0.05</v>
+        <v>3.73</v>
       </c>
       <c r="N52" t="n">
-        <v>0.41</v>
+        <v>3.22</v>
       </c>
       <c r="O52" t="n">
         <v>2.02</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>3.83</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45938.55208333334</v>
+        <v>45939.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1419.7</v>
+        <v>1435.7</v>
       </c>
       <c r="I53" t="n">
         <v>1428.644214008352</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>2.61</v>
+        <v>1.51</v>
       </c>
       <c r="L53" t="n">
         <v>1.08</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.14</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1383.7</v>
+        <v>1375.7</v>
       </c>
       <c r="I54" t="n">
         <v>1381.448402105234</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.62</v>
+        <v>-4.18</v>
       </c>
       <c r="L54" t="n">
-        <v>4.01</v>
+        <v>4.58</v>
       </c>
       <c r="M54" t="n">
         <v>0.42</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>3.46</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1371.2</v>
+        <v>1421.4</v>
       </c>
       <c r="I55" t="n">
         <v>1396.982758295455</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>0.33</v>
+        <v>-3.32</v>
       </c>
       <c r="L55" t="n">
-        <v>0.98</v>
+        <v>3.45</v>
       </c>
       <c r="M55" t="n">
         <v>0.59</v>
       </c>
       <c r="N55" t="n">
-        <v>0.72</v>
+        <v>3.57</v>
       </c>
       <c r="O55" t="n">
         <v>-0.84</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.11</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46022.38541666666</v>
+        <v>46022.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1560.7</v>
+        <v>1550.7</v>
       </c>
       <c r="I56" t="n">
         <v>1551.367662831017</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="L56" t="n">
         <v>3.04</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>3.3</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46036.55208333334</v>
+        <v>46038.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1551.9</v>
+        <v>1621.3</v>
       </c>
       <c r="I57" t="n">
         <v>1601.839526538217</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.08</v>
+        <v>-4.55</v>
       </c>
       <c r="L57" t="n">
-        <v>2.7</v>
+        <v>4.97</v>
       </c>
       <c r="M57" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="N57" t="n">
-        <v>1.89</v>
+        <v>5.01</v>
       </c>
       <c r="O57" t="n">
         <v>-0.74</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.46</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1669.3</v>
+        <v>1577.4</v>
       </c>
       <c r="I58" t="n">
         <v>1656.967271323865</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K58" t="n">
-        <v>2.96</v>
+        <v>-2.71</v>
       </c>
       <c r="L58" t="n">
-        <v>3.81</v>
+        <v>3.94</v>
       </c>
       <c r="M58" t="n">
-        <v>0.51</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
-        <v>2.03</v>
+        <v>4.3</v>
       </c>
       <c r="O58" t="n">
         <v>5.01</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.58</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46104.55208333334</v>
+        <v>46105.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1353.8</v>
+        <v>1387.7</v>
       </c>
       <c r="I59" t="n">
         <v>1365.655638397964</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K59" t="n">
-        <v>14.18</v>
+        <v>12.03</v>
       </c>
       <c r="L59" t="n">
         <v>2.52</v>
@@ -3804,7 +4511,7 @@
         <v>2.05</v>
       </c>
       <c r="N59" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="O59" t="n">
         <v>-4.3</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.22</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46133.55208333334</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1461</v>
+        <v>1379.1</v>
       </c>
       <c r="I60" t="n">
         <v>1399.77164249989</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K60" t="n">
-        <v>5.28</v>
+        <v>-0.62</v>
       </c>
       <c r="L60" t="n">
         <v>3.98</v>
       </c>
       <c r="M60" t="n">
-        <v>1.12</v>
+        <v>2.38</v>
       </c>
       <c r="N60" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="O60" t="n">
         <v>3.17</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.26</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46142.38541666666</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1429.6</v>
+        <v>1438.6</v>
       </c>
       <c r="I61" t="n">
         <v>1436.792275850359</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.66</v>
+        <v>-4.31</v>
       </c>
       <c r="L61" t="n">
         <v>6.21</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>6.3</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46154.55208333334</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1360.6</v>
+        <v>1344.8</v>
       </c>
       <c r="I62" t="n">
         <v>1357.960867857796</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>-5.42</v>
+        <v>-6.52</v>
       </c>
       <c r="L62" t="n">
-        <v>5.9</v>
+        <v>7.07</v>
       </c>
       <c r="M62" t="n">
         <v>0.75</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.04</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1334.3</v>
+        <v>1391.7</v>
       </c>
       <c r="I63" t="n">
         <v>1387.595111173076</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>0.78</v>
+        <v>-3.49</v>
       </c>
       <c r="L63" t="n">
-        <v>1.46</v>
+        <v>3.73</v>
       </c>
       <c r="M63" t="n">
         <v>0.66</v>
       </c>
       <c r="N63" t="n">
-        <v>2.07</v>
+        <v>4.83</v>
       </c>
       <c r="O63" t="n">
         <v>-1.5</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8.66</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1530.3</v>
+        <v>1442.5</v>
       </c>
       <c r="I64" t="n">
         <v>1446.479061288191</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K64" t="n">
-        <v>9.960000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="L64" t="n">
         <v>4.49</v>
       </c>
       <c r="M64" t="n">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="N64" t="n">
-        <v>1.9</v>
+        <v>6.37</v>
       </c>
       <c r="O64" t="n">
         <v>4.83</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.68</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1389.9</v>
+        <v>1429.9</v>
       </c>
       <c r="I65" t="n">
         <v>1404.352238543524</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K65" t="n">
-        <v>3.65</v>
+        <v>0.87</v>
       </c>
       <c r="L65" t="n">
         <v>5.05</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.91</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46253.38541666666</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1585.4</v>
+        <v>1583</v>
       </c>
       <c r="I66" t="n">
         <v>1583.101704016546</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K66" t="n">
-        <v>10.87</v>
+        <v>10.71</v>
       </c>
       <c r="L66" t="n">
         <v>2.72</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>4.07</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="I67" t="n">
         <v>1638.22036370657</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.34</v>
+        <v>-3.73</v>
       </c>
       <c r="L67" t="n">
-        <v>3.73</v>
+        <v>4.17</v>
       </c>
       <c r="M67" t="n">
         <v>1.17</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>5.14</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1587.7</v>
+        <v>1549.6</v>
       </c>
       <c r="I68" t="n">
         <v>1566.187425452048</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.31</v>
+        <v>-5.63</v>
       </c>
       <c r="L68" t="n">
-        <v>3.36</v>
+        <v>5.65</v>
       </c>
       <c r="M68" t="n">
-        <v>0.35</v>
+        <v>0.79</v>
       </c>
       <c r="N68" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="O68" t="n">
         <v>0.98</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>6.16</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1538.9</v>
+        <v>1587.3</v>
       </c>
       <c r="I69" t="n">
         <v>1575.52573512292</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K69" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.43</v>
       </c>
       <c r="L69" t="n">
-        <v>2.84</v>
+        <v>5.39</v>
       </c>
       <c r="M69" t="n">
-        <v>0.59</v>
+        <v>3.19</v>
       </c>
       <c r="N69" t="n">
-        <v>1.23</v>
+        <v>2.51</v>
       </c>
       <c r="O69" t="n">
         <v>-1.93</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>4.54</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1532</v>
+        <v>1499.5</v>
       </c>
       <c r="I70" t="n">
         <v>1515.270067167267</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.48</v>
+        <v>-5.53</v>
       </c>
       <c r="L70" t="n">
-        <v>4.89</v>
+        <v>5.79</v>
       </c>
       <c r="M70" t="n">
         <v>0.92</v>
       </c>
       <c r="N70" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="O70" t="n">
         <v>2.51</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.76</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1538.9</v>
+        <v>1551.2</v>
       </c>
       <c r="I71" t="n">
         <v>1544.425442119779</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.63</v>
+        <v>-3.45</v>
       </c>
       <c r="L71" t="n">
-        <v>2.82</v>
+        <v>4.48</v>
       </c>
       <c r="M71" t="n">
         <v>0.99</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,14 @@
       <c r="Q72" t="n">
         <v>20</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6650,7 +7521,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="6">
@@ -6660,7 +7531,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.7</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="7">
@@ -6670,7 +7541,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="8">
@@ -6680,7 +7551,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6690,7 +7561,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -6700,7 +7571,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -6740,7 +7611,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.46</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="15">
@@ -6750,7 +7621,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.31</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -6760,7 +7631,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.62</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="17">
@@ -6770,7 +7641,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.05</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="18">
@@ -6780,7 +7651,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62.9</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="19">
@@ -6790,7 +7661,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.35</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="20">
@@ -6800,7 +7671,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.16</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="21">
@@ -6810,7 +7681,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.85</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="22">
@@ -6820,7 +7691,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -6840,7 +7711,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25">
@@ -6850,7 +7721,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.37</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="26">
@@ -6860,7 +7731,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.59</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="27">
@@ -6870,7 +7741,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.81</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="28">
@@ -6880,7 +7751,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
